--- a/apps/web/public/import-templates/players-template-en.xlsx
+++ b/apps/web/public/import-templates/players-template-en.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="jugadores" sheetId="1" r:id="rId1"/>
-    <sheet name="Guide" sheetId="2" r:id="rId2"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +17,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>Full name*</t>
+    <t>First name*</t>
+  </si>
+  <si>
+    <t>Surname</t>
   </si>
   <si>
     <t>Date of birth*</t>
@@ -29,7 +32,10 @@
     <t>Email*</t>
   </si>
   <si>
-    <t>Pepe Gómez García</t>
+    <t>Pepe</t>
+  </si>
+  <si>
+    <t>Gómez García</t>
   </si>
   <si>
     <t>15/03/2010</t>
@@ -41,7 +47,10 @@
     <t>pepe.gomez@example.com</t>
   </si>
   <si>
-    <t>Lucía Sánchez López</t>
+    <t>Lucía</t>
+  </si>
+  <si>
+    <t>Sánchez López</t>
   </si>
   <si>
     <t>03/09/2011</t>
@@ -53,7 +62,10 @@
     <t>familia.lucia@example.com</t>
   </si>
   <si>
-    <t>Mario Ruiz</t>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
   </si>
   <si>
     <t>20/01/2012</t>
@@ -68,19 +80,22 @@
     <t>How to fill it in</t>
   </si>
   <si>
-    <t>Full name</t>
-  </si>
-  <si>
-    <t>Required. Player’s first name and surname in a single cell (e.g. "Pepe Gómez García").</t>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Required. The given name ONLY (e.g. "Pepe"). Surnames go in their own column.</t>
+  </si>
+  <si>
+    <t>Optional. The surnames, in their own column (e.g. "Gómez García"). Leave it empty if the player only has a given name.</t>
   </si>
   <si>
     <t>Date of birth</t>
   </si>
   <si>
-    <t>Required. Preferred format dd/mm/yyyy (e.g. 15/03/2010). Also dd-mm-yyyy, yyyy-mm-dd or an Excel cell with Date format.</t>
-  </si>
-  <si>
-    <t>Optional. EXACT name of an existing team in the active season (e.g. "Infantil A"). If left empty, the team chosen in the wizard is used. A team that does not exist gives an error (the import does not create teams).</t>
+    <t>Required. Preferred format dd/mm/yyyy (e.g. 15/03/2010). Also dd-mm-yyyy, yyyy-mm-dd or an Excel cell formatted as Date.</t>
+  </si>
+  <si>
+    <t>Optional. The EXACT name of an existing team in the active season (e.g. "Infantil A"). If left empty, the team picked in the wizard is used. A team that does not exist is an error (importing never creates teams).</t>
   </si>
   <si>
     <t>Email</t>
@@ -106,15 +121,27 @@
       <color theme="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBF7D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,9 +149,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9CA3AF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9CA3AF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9CA3AF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9CA3AF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf/>
+    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="3" applyFill="1"/>
     <xf fontId="1" applyFont="1"/>
   </cellXfs>
 </styleSheet>
@@ -137,53 +186,65 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -194,43 +255,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>17</v>
+      <c r="A2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>19</v>
+      <c r="A3" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>2</v>
+      <c r="A4" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>22</v>
+      <c r="A5" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
